--- a/patiencestudy.xlsx
+++ b/patiencestudy.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yhe\Desktop\PHD\Research\26spring_Global_View\26spring_Global_View_project\Cash-or-Comfort-How-LLMs-Value-Your-Inconvenience\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB722C3-EF2E-4118-A7BB-A51C475B4ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F567472-DB23-4BBE-B779-FE1D33F6169B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
